--- a/data/dummy_output.xlsx
+++ b/data/dummy_output.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://camsys-my.sharepoint.com/personal/qsi_camsys_com/Documents/Desktop/TEA-CART/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://camsys-my.sharepoint.com/personal/slarue_camsys_com/Documents/Documents/idot_github_puller/TEACART/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F35018-F94F-4C7F-B8C6-7FAD62D7D49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{13F35018-F94F-4C7F-B8C6-7FAD62D7D49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{315B7CEA-1F8D-47ED-9436-E3AB3A9712CF}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-24" windowWidth="23256" windowHeight="12252" xr2:uid="{A690EF85-1435-408F-9A1C-82335AE580D8}"/>
+    <workbookView xWindow="270" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{A690EF85-1435-408F-9A1C-82335AE580D8}"/>
   </bookViews>
   <sheets>
     <sheet name="GHG Forecast" sheetId="1" r:id="rId1"/>
@@ -42,12 +42,6 @@
     <t>Emissions (MT CO2e)</t>
   </si>
   <si>
-    <t>Light Duty Vehicles</t>
-  </si>
-  <si>
-    <t>Medium and Heavy Duty Trucks</t>
-  </si>
-  <si>
     <t>Public Transit</t>
   </si>
   <si>
@@ -76,6 +70,12 @@
   </si>
   <si>
     <t>Scenario 2</t>
+  </si>
+  <si>
+    <t>Light-Duty Vehicles</t>
+  </si>
+  <si>
+    <t>Medium- and Heavy-Duty Trucks</t>
   </si>
 </sst>
 </file>
@@ -131,9 +131,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -171,7 +171,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -277,7 +277,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -419,7 +419,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -428,14 +428,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BF74F51-1937-4600-A70B-F95A7B6D19B1}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -452,9 +452,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>16926660.57603753</v>
@@ -469,9 +469,9 @@
         <v>16561170.578931591</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>5594752.0342581868</v>
@@ -486,9 +486,9 @@
         <v>5261934.5163450828</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4">
         <v>120934.11023762191</v>
@@ -503,9 +503,9 @@
         <v>120934.11023762191</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5">
         <v>76608.001955410116</v>
@@ -520,9 +520,9 @@
         <v>76608.001955410116</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6">
         <v>56162.315418065504</v>
@@ -537,9 +537,9 @@
         <v>68485.375676508644</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -554,9 +554,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>22521412.610295717</v>
@@ -571,9 +571,9 @@
         <v>21823105.095276672</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>22775117.037906811</v>
@@ -588,9 +588,9 @@
         <v>22089132.583146211</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>3.1535435195681145E-2</v>
@@ -610,9 +610,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B2A338-5198-4886-9C4F-D0BB12CC89BE}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -629,9 +629,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>22661102.84583756</v>
@@ -646,9 +646,9 @@
         <v>21980833.534987621</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>22661102.84583756</v>
@@ -663,9 +663,9 @@
         <v>21854870.347187866</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>22661102.84583756</v>
